--- a/data/google_news_dedup_audit_24_0426_UTC.xlsx
+++ b/data/google_news_dedup_audit_24_0426_UTC.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,370 +445,370 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8914639949798584</v>
+        <v>0.7155748009681702</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Royal Mail issues delivery delay warning to anyone in 13 postcodes — full list - The Mirror</t>
+          <t>M&amp;S chairman blames self-service checkouts for rise in shoplifting - Wandsworth Times</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>UK Postcodes Update: Royal Mail Issued a Warning of Delivery Delays in 13 Postcodes | Check the full Postcodes list - The Sunday Guardian</t>
+          <t>M&amp;S boss blames major change in supermarkets for huge rise in shoplifting - Daily Express</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8257026076316833</v>
+        <v>0.8599234819412231</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Royal Mail issues delivery delay warning to anyone in 13 postcodes — full list - The Mirror</t>
+          <t>Op zucht van promotie naar 1B, maar Sporting Hasselt krijgt geen proflicentie: "We zijn positief voor beroepsprocedure" - sporza.be</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Royal Mail delivery delays hit 13 UK postcodes today — full list of affected areas - Daily Express</t>
+          <t>Op zucht van promotie naar 1B, maar Sporting Hasselt krijgt geen proflicentie: "Goede hoop op beroepsprocedure" - sporza.be</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7715407609939575</v>
+        <v>0.7348417043685913</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Amazon introduces 1-hour and 3-hour delivery in US - MSN</t>
+          <t>Op zucht van promotie naar 1B, maar Sporting Hasselt krijgt geen proflicentie: "We zijn positief voor beroepsprocedure" - sporza.be</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>The delivery speed wars are heating up as Amazon rolls out 1-hour delivery - MSN</t>
+          <t>SK Roeselare heeft licentie voor profvoetbal beet en staat (mogelijk) op één gelijkspel van promotie naar 1B: “Bewijs dat we op de goede weg zijn” - Nieuwsblad</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B5" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7844200134277344</v>
+        <v>0.6331067085266113</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>FedEx joins Amazon, Walmart in race to get goods to Americans faster with new same-day delivery service - MSN</t>
+          <t>Sporting Hasselt krijgt geen licentie voor 1B - Nieuwsblad</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FedEx launches same-day delivery with OneRail as Amazon, Walmart boost their speeds - MSN</t>
+          <t>Uitverkochte titelmatch van Sporting Hasselt zorgt voor primeur bij politie - Voetbalkrant.com</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8986888527870178</v>
+        <v>0.7289161086082458</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>20-Jähriger löst erneut Polizeieinsatz aus und wird in Klinik eingewiesen - Augsburger Allgemeine</t>
+          <t>Sporting Hasselt krijgt geen licentie voor 1B - Nieuwsblad</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>20-Jähriger löst mehrere Polizeieinsätze aus und wird festgenommen - Augsburger Allgemeine</t>
+          <t>Bijna kampioen, maar geen licentie: cultclub Sporting Hasselt mag (nog) niet promoveren naar 1B - HLN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="B7" t="n">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="C7" t="n">
-        <v>1.00000011920929</v>
+        <v>0.7216100096702576</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Gabriel Bortoleto visits Audi in Ingolstadt - Audi MediaCenter</t>
+          <t>Sporting Hasselt krijgt geen licentie voor 1B - Nieuwsblad</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gabriel Bortoleto visits Audi in Ingolstadt - Audi MediaCenter</t>
+          <t>Sporting Hasselt kan zondag kampioen spelen, maar krijgt voorlopig geen licentie voor 1B - TV Limburg</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="B8" t="n">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7642118334770203</v>
+        <v>0.8208534717559814</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Young man stabbed to death after 'altercation' in east London street - London Evening Standard</t>
+          <t>Sporting Hasselt krijgt geen licentie voor 1B - Nieuwsblad</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Man dies after stabbing on busy road outside shops - London Now</t>
+          <t>Sporting Hasselt krijgt geen licentie voor 1B, ook SK Tongeren vangt bot in tweede zit - HBVL</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="B9" t="n">
-        <v>64</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7832018136978149</v>
+        <v>0.7798896431922913</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>In arrivo uno sciopero Atm a Milano: gli orari di metro, bus e tram (e le fasce di garanzia) - MilanoToday</t>
+          <t>Sporting Hasselt krijgt geen licentie voor 1B - Nieuwsblad</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sciopero Atm oggi, venerdì 24 aprile 2026: metro, bus e tram a rischio. Orari e fasce di garanzia - Il Giorno</t>
+          <t>Geen licentie voor Sporting Hasselt - VoetbalBelgie</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="B10" t="n">
-        <v>65</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6821703910827637</v>
+        <v>0.8627288937568665</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>In arrivo uno sciopero Atm a Milano: gli orari di metro, bus e tram (e le fasce di garanzia) - MilanoToday</t>
+          <t>Sporting Hasselt krijgt geen licentie voor 1B - Nieuwsblad</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sciopero dei trasporti a Milano, arrivano i disagi: orari e corse garantite in Lombardia - Moveo by Telepass</t>
+          <t>Ze kunnen zondag kampioen worden, maar Sporting Hasselt krijgt (nog) geen licentie voor 1B - Nieuwsblad</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="B11" t="n">
-        <v>66</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6633086204528809</v>
+        <v>0.6569637060165405</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>In arrivo uno sciopero Atm a Milano: gli orari di metro, bus e tram (e le fasce di garanzia) - MilanoToday</t>
+          <t>Sporting Hasselt krijgt geen licentie voor 1B - Nieuwsblad</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sciopero 24 aprile, a Milano i mezzi pubblici si fermano per mezza giornata: quali sono le linee Atm garantite - Virgilio</t>
+          <t>Bijna kampioen, maar geen licentie: showbizzclub Sporting Hasselt mag (nog) niet promoveren naar 1B | Foto - HLN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="B12" t="n">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5948742628097534</v>
+        <v>0.7819396257400513</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>In arrivo uno sciopero Atm a Milano: gli orari di metro, bus e tram (e le fasce di garanzia) - MilanoToday</t>
+          <t>26-jarige student schuldig aan verkrachting studente, maar hij krijgt geen straf - VRT</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>25 aprile. Fumarola sabato a manifestazione a Milano per l’81° della Liberazione - firstcisl.it</t>
+          <t>Schachtentemmer schuldig aan verkrachting van studente in Hasselt krijgt opschorting van straf - De Morgen</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="B13" t="n">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6722919344902039</v>
+        <v>0.8146485686302185</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>In arrivo uno sciopero Atm a Milano: gli orari di metro, bus e tram (e le fasce di garanzia) - MilanoToday</t>
+          <t>Schwerpunktkontrolle nächste Woche: Polizei überprüft Zweiräder im Stadtgebiet - Augsburger Allgemeine</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sciopero dei mezzi a Milano il 24 aprile: quando circolano le linee - Mi-Tomorrow</t>
+          <t>Polizei schnappt 16-Jährigen ohne Führerschein bei Spritztour - Augsburger Allgemeine</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="B14" t="n">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6905781030654907</v>
+        <v>0.7640090584754944</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>In arrivo uno sciopero Atm a Milano: gli orari di metro, bus e tram (e le fasce di garanzia) - MilanoToday</t>
+          <t>Audi revamps production, ends A1 and Q2 lines - Just Auto</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>25 Aprile diviso a Milano: polemica sulla Brigata ebraica e corteo sdoppiato - milanopavia.news</t>
+          <t>Audi A1 And Q2 Production Ends Ahead Of The A2's Return - Motor1.com</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="B15" t="n">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6274346113204956</v>
+        <v>0.8628928661346436</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>In arrivo uno sciopero Atm a Milano: gli orari di metro, bus e tram (e le fasce di garanzia) - MilanoToday</t>
+          <t>Waymo 'driverless' taxi ploughs into London crime scene after double stabbing - London Evening Standard</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Un corteo e due piazze a Milano il 25 aprile, Sala: "Nulla da dire sulla seconda piazza" - Radio Lombardia</t>
+          <t>'Driverless’ taxi crashes into London crime scene as detectives probe double stabbing - lbc.co.uk</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="B16" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6791418790817261</v>
+        <v>0.8024270534515381</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>In arrivo uno sciopero Atm a Milano: gli orari di metro, bus e tram (e le fasce di garanzia) - MilanoToday</t>
+          <t>Waymo 'driverless' taxi ploughs into London crime scene after double stabbing - London Evening Standard</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Metrotranvia Milano-Seregno, mancano 120 milioni: i cantieri si fermano e scoppia la protesta - MilanoToday</t>
+          <t>'Driverless' Waymo taxi ploughs into Harlesden double stabbing cordon - My London</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="B17" t="n">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6756464838981628</v>
+        <v>0.8404362201690674</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>In arrivo uno sciopero Atm a Milano: gli orari di metro, bus e tram (e le fasce di garanzia) - MilanoToday</t>
+          <t>Waymo 'driverless' taxi ploughs into London crime scene after double stabbing - London Evening Standard</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Disagi a Milano e in Lombardia per lo sciopero dei mezzi - Moveo by Telepass</t>
+          <t>Footage shows the moment driverless taxi crashes into double stabbing crime scene - London Now</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="B18" t="n">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6200555562973022</v>
+        <v>0.7273826599121094</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>In arrivo uno sciopero Atm a Milano: gli orari di metro, bus e tram (e le fasce di garanzia) - MilanoToday</t>
+          <t>London's latest Tube strike revealed to be union's least effective in YEARS - GB News</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Milano, Sala: sarà un 25 aprile delicato. Anpi: errore rompere unità del fronte antifascista - Il Giorno</t>
+          <t>Travel disruption in London as Tube strike continues - lbc.co.uk</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B19" t="n">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6880326867103577</v>
+        <v>0.7832018136978149</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -817,19 +817,19 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Confermato lo sciopero Atm a Milano e in Lombardia, stop ai mezzi pubblici domani: orari e fasce garantite - Moveo by Telepass</t>
+          <t>Sciopero Atm oggi, venerdì 24 aprile 2026: metro, bus e tram a rischio. Orari e fasce di garanzia - Il Giorno</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B20" t="n">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7034307718276978</v>
+        <v>0.6835035085678101</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -838,91 +838,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Atm Milano, sciopero il 24 aprile: stop a metro e mezzi nel venerdì della Design Week - Mentelocale</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>63</v>
-      </c>
-      <c r="B21" t="n">
-        <v>82</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0.6682213544845581</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>In arrivo uno sciopero Atm a Milano: gli orari di metro, bus e tram (e le fasce di garanzia) - MilanoToday</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Design weekend del 25 e 26 aprile a Milano, cosa fare? Sagre, corteo, installazioni del Fuorisalone, musei gratis - Mentelocale</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>63</v>
-      </c>
-      <c r="B22" t="n">
-        <v>83</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0.609890341758728</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>In arrivo uno sciopero Atm a Milano: gli orari di metro, bus e tram (e le fasce di garanzia) - MilanoToday</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Sciopero dei trasporti venerdì 24 aprile, a rischio metropolitane e autobus: gli orari e le fasce - Virgilio</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>63</v>
-      </c>
-      <c r="B23" t="n">
-        <v>84</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0.6787501573562622</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>In arrivo uno sciopero Atm a Milano: gli orari di metro, bus e tram (e le fasce di garanzia) - MilanoToday</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Weekend del 25-26 aprile a Milano: sagre, corteo, Fuorisalone e musei - inItaly</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>68</v>
-      </c>
-      <c r="B24" t="n">
-        <v>72</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0.7170571088790894</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>25 aprile a Bologna, il programma tra cerimonie istituzionali e concerti. Corteo da piazza dell’Unità - Il Resto del Carlino</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Festa il 25 aprile, fra cortei, spettacoli e concerti - vivimilano.corriere.it</t>
+          <t>Sciopero Atm MIlano oggi 24 aprile, chi si ferma e orario stop - CN24TV</t>
         </is>
       </c>
     </row>
